--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:07</t>
+    <t xml:space="preserve">2026-09-24 00:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -773,7 +773,7 @@
         <v>-0.8</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19">
@@ -787,7 +787,7 @@
         <v>-0.33</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20">
@@ -801,7 +801,7 @@
         <v>-0.63</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21">
@@ -815,7 +815,7 @@
         <v>-0.32</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:58</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2020.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
